--- a/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
@@ -112,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -181,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,19 +717,19 @@
   <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1443,29 +1581,29 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>Población total</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>Densidad poblacional (hab/km²)</t>
         </is>
@@ -1691,185 +1829,185 @@
   <dimension ref="A1:AG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1894,91 +2032,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>6159</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>6031</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>1874</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>1969</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>1788</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>1829</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>1518</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>1214</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>1150</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>602</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>246</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>979</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>1008</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>926</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>953</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>766</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>570</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>543</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>293</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>121</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>895</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>961</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>862</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>876</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>752</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>644</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>607</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>309</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>125</v>
       </c>
     </row>
@@ -2001,91 +2139,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>10451</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>9361</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>3729</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>3519</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>3332</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>3105</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>2349</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>1599</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>1191</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>694</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>294</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>1883</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>1863</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>1769</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>1685</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>1254</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>831</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>635</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>361</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>170</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>1846</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>1656</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>1563</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>1420</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>1095</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>768</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>556</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>333</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>124</v>
       </c>
     </row>
@@ -2108,91 +2246,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>4490</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>4109</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>1622</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>1544</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>1276</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>1322</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>1028</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>766</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>591</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>318</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>132</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>829</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>827</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>652</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>656</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>556</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>407</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>323</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>170</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>70</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>793</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>717</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>624</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>666</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>472</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>359</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>268</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>148</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>62</v>
       </c>
     </row>
@@ -2215,91 +2353,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>5063</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>4776</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>1658</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>1785</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>1375</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>1404</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>1180</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>927</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>799</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>486</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>225</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>848</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>956</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>704</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>701</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>613</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>460</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>407</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>252</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>122</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>810</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>829</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>671</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>703</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>567</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>467</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>392</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>234</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>103</v>
       </c>
     </row>
@@ -2322,91 +2460,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>2077</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>2165</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>369</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>508</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>520</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>584</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>595</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>637</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>543</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>340</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>146</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>193</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>261</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>286</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>296</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>292</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>300</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>243</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>151</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>55</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>176</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>247</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>234</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>288</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>303</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>337</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>300</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>189</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>91</v>
       </c>
     </row>
@@ -2429,91 +2567,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="25">
         <v>5155</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <v>5309</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <v>1232</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="31">
         <v>1389</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>1220</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="35">
         <v>1489</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="37">
         <v>1432</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="39">
         <v>1334</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="41">
         <v>1249</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="43">
         <v>749</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="45">
         <v>370</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="47">
         <v>600</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="49">
         <v>742</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="51">
         <v>605</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="53">
         <v>703</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="55">
         <v>723</v>
       </c>
-      <c r="U7" s="54">
+      <c r="U7" s="57">
         <v>648</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="59">
         <v>608</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="61">
         <v>348</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="63">
         <v>178</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="65">
         <v>632</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="Z7" s="67">
         <v>647</v>
       </c>
-      <c r="AA7" s="66">
+      <c r="AA7" s="69">
         <v>615</v>
       </c>
-      <c r="AB7" s="68">
+      <c r="AB7" s="71">
         <v>786</v>
       </c>
-      <c r="AC7" s="70">
+      <c r="AC7" s="73">
         <v>709</v>
       </c>
-      <c r="AD7" s="72">
+      <c r="AD7" s="75">
         <v>686</v>
       </c>
-      <c r="AE7" s="74">
+      <c r="AE7" s="77">
         <v>641</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="79">
         <v>401</v>
       </c>
-      <c r="AG7" s="78">
+      <c r="AG7" s="81">
         <v>192</v>
       </c>
     </row>
@@ -2536,91 +2674,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <v>3567</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="27">
         <v>3448</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <v>984</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="31">
         <v>1093</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="33">
         <v>1008</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="35">
         <v>1075</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="37">
         <v>951</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="39">
         <v>738</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="41">
         <v>637</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="43">
         <v>377</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="45">
         <v>152</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="47">
         <v>523</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="49">
         <v>552</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="51">
         <v>507</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="53">
         <v>566</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="55">
         <v>493</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="57">
         <v>362</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="59">
         <v>297</v>
       </c>
-      <c r="W8" s="58">
+      <c r="W8" s="61">
         <v>186</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="63">
         <v>81</v>
       </c>
-      <c r="Y8" s="62">
+      <c r="Y8" s="65">
         <v>461</v>
       </c>
-      <c r="Z8" s="64">
+      <c r="Z8" s="67">
         <v>541</v>
       </c>
-      <c r="AA8" s="66">
+      <c r="AA8" s="69">
         <v>501</v>
       </c>
-      <c r="AB8" s="68">
+      <c r="AB8" s="71">
         <v>509</v>
       </c>
-      <c r="AC8" s="70">
+      <c r="AC8" s="73">
         <v>458</v>
       </c>
-      <c r="AD8" s="72">
+      <c r="AD8" s="75">
         <v>376</v>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="77">
         <v>340</v>
       </c>
-      <c r="AF8" s="76">
+      <c r="AF8" s="79">
         <v>191</v>
       </c>
-      <c r="AG8" s="78">
+      <c r="AG8" s="81">
         <v>71</v>
       </c>
     </row>
@@ -2643,91 +2781,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="25">
         <v>17547</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="27">
         <v>11527</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <v>4011</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="31">
         <v>4293</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="33">
         <v>4836</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="35">
         <v>5307</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="37">
         <v>4218</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="39">
         <v>2922</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="41">
         <v>1895</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="43">
         <v>1130</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="45">
         <v>462</v>
       </c>
-      <c r="P9" s="44">
+      <c r="P9" s="47">
         <v>1980</v>
       </c>
-      <c r="Q9" s="46">
+      <c r="Q9" s="49">
         <v>2290</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="51">
         <v>3091</v>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="53">
         <v>3579</v>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="55">
         <v>2793</v>
       </c>
-      <c r="U9" s="54">
+      <c r="U9" s="57">
         <v>1897</v>
       </c>
-      <c r="V9" s="56">
+      <c r="V9" s="59">
         <v>1096</v>
       </c>
-      <c r="W9" s="58">
+      <c r="W9" s="61">
         <v>592</v>
       </c>
-      <c r="X9" s="60">
+      <c r="X9" s="63">
         <v>229</v>
       </c>
-      <c r="Y9" s="62">
+      <c r="Y9" s="65">
         <v>2031</v>
       </c>
-      <c r="Z9" s="64">
+      <c r="Z9" s="67">
         <v>2003</v>
       </c>
-      <c r="AA9" s="66">
+      <c r="AA9" s="69">
         <v>1745</v>
       </c>
-      <c r="AB9" s="68">
+      <c r="AB9" s="71">
         <v>1728</v>
       </c>
-      <c r="AC9" s="70">
+      <c r="AC9" s="73">
         <v>1425</v>
       </c>
-      <c r="AD9" s="72">
+      <c r="AD9" s="75">
         <v>1025</v>
       </c>
-      <c r="AE9" s="74">
+      <c r="AE9" s="77">
         <v>799</v>
       </c>
-      <c r="AF9" s="76">
+      <c r="AF9" s="79">
         <v>538</v>
       </c>
-      <c r="AG9" s="78">
+      <c r="AG9" s="81">
         <v>233</v>
       </c>
     </row>
@@ -2750,91 +2888,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <v>3945</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="27">
         <v>3752</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <v>1389</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="31">
         <v>1288</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="33">
         <v>1121</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="35">
         <v>1098</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="37">
         <v>899</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="39">
         <v>774</v>
       </c>
-      <c r="M10" s="38">
+      <c r="M10" s="41">
         <v>631</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="43">
         <v>353</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="45">
         <v>144</v>
       </c>
-      <c r="P10" s="44">
+      <c r="P10" s="47">
         <v>714</v>
       </c>
-      <c r="Q10" s="46">
+      <c r="Q10" s="49">
         <v>669</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R10" s="51">
         <v>564</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="53">
         <v>573</v>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="55">
         <v>469</v>
       </c>
-      <c r="U10" s="54">
+      <c r="U10" s="57">
         <v>392</v>
       </c>
-      <c r="V10" s="56">
+      <c r="V10" s="59">
         <v>321</v>
       </c>
-      <c r="W10" s="58">
+      <c r="W10" s="61">
         <v>173</v>
       </c>
-      <c r="X10" s="60">
+      <c r="X10" s="63">
         <v>70</v>
       </c>
-      <c r="Y10" s="62">
+      <c r="Y10" s="65">
         <v>675</v>
       </c>
-      <c r="Z10" s="64">
+      <c r="Z10" s="67">
         <v>619</v>
       </c>
-      <c r="AA10" s="66">
+      <c r="AA10" s="69">
         <v>557</v>
       </c>
-      <c r="AB10" s="68">
+      <c r="AB10" s="71">
         <v>525</v>
       </c>
-      <c r="AC10" s="70">
+      <c r="AC10" s="73">
         <v>430</v>
       </c>
-      <c r="AD10" s="72">
+      <c r="AD10" s="75">
         <v>382</v>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="77">
         <v>310</v>
       </c>
-      <c r="AF10" s="76">
+      <c r="AF10" s="79">
         <v>180</v>
       </c>
-      <c r="AG10" s="78">
+      <c r="AG10" s="81">
         <v>74</v>
       </c>
     </row>
@@ -2857,91 +2995,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="25">
         <v>1919</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="27">
         <v>2022</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <v>634</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="31">
         <v>711</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="33">
         <v>608</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="35">
         <v>589</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="37">
         <v>498</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="39">
         <v>403</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="41">
         <v>289</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="43">
         <v>157</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="45">
         <v>52</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="47">
         <v>278</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="49">
         <v>331</v>
       </c>
-      <c r="R11" s="48">
+      <c r="R11" s="51">
         <v>320</v>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="53">
         <v>295</v>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="55">
         <v>267</v>
       </c>
-      <c r="U11" s="54">
+      <c r="U11" s="57">
         <v>202</v>
       </c>
-      <c r="V11" s="56">
+      <c r="V11" s="59">
         <v>136</v>
       </c>
-      <c r="W11" s="58">
+      <c r="W11" s="61">
         <v>68</v>
       </c>
-      <c r="X11" s="60">
+      <c r="X11" s="63">
         <v>22</v>
       </c>
-      <c r="Y11" s="62">
+      <c r="Y11" s="65">
         <v>356</v>
       </c>
-      <c r="Z11" s="64">
+      <c r="Z11" s="67">
         <v>380</v>
       </c>
-      <c r="AA11" s="66">
+      <c r="AA11" s="69">
         <v>288</v>
       </c>
-      <c r="AB11" s="68">
+      <c r="AB11" s="71">
         <v>294</v>
       </c>
-      <c r="AC11" s="70">
+      <c r="AC11" s="73">
         <v>231</v>
       </c>
-      <c r="AD11" s="72">
+      <c r="AD11" s="75">
         <v>201</v>
       </c>
-      <c r="AE11" s="74">
+      <c r="AE11" s="77">
         <v>153</v>
       </c>
-      <c r="AF11" s="76">
+      <c r="AF11" s="79">
         <v>89</v>
       </c>
-      <c r="AG11" s="78">
+      <c r="AG11" s="81">
         <v>30</v>
       </c>
     </row>
@@ -2964,91 +3102,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="25">
         <v>2806</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="27">
         <v>2490</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <v>925</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="31">
         <v>851</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="33">
         <v>742</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="35">
         <v>891</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="37">
         <v>644</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="39">
         <v>442</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12" s="41">
         <v>427</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="43">
         <v>241</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="45">
         <v>133</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="47">
         <v>500</v>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="49">
         <v>443</v>
       </c>
-      <c r="R12" s="48">
+      <c r="R12" s="51">
         <v>397</v>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="53">
         <v>477</v>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="55">
         <v>347</v>
       </c>
-      <c r="U12" s="54">
+      <c r="U12" s="57">
         <v>236</v>
       </c>
-      <c r="V12" s="56">
+      <c r="V12" s="59">
         <v>219</v>
       </c>
-      <c r="W12" s="58">
+      <c r="W12" s="61">
         <v>122</v>
       </c>
-      <c r="X12" s="60">
+      <c r="X12" s="63">
         <v>65</v>
       </c>
-      <c r="Y12" s="62">
+      <c r="Y12" s="65">
         <v>425</v>
       </c>
-      <c r="Z12" s="64">
+      <c r="Z12" s="67">
         <v>408</v>
       </c>
-      <c r="AA12" s="66">
+      <c r="AA12" s="69">
         <v>345</v>
       </c>
-      <c r="AB12" s="68">
+      <c r="AB12" s="71">
         <v>414</v>
       </c>
-      <c r="AC12" s="70">
+      <c r="AC12" s="73">
         <v>297</v>
       </c>
-      <c r="AD12" s="72">
+      <c r="AD12" s="75">
         <v>206</v>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="77">
         <v>208</v>
       </c>
-      <c r="AF12" s="76">
+      <c r="AF12" s="79">
         <v>119</v>
       </c>
-      <c r="AG12" s="78">
+      <c r="AG12" s="81">
         <v>68</v>
       </c>
     </row>
@@ -3071,91 +3209,91 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="25">
         <v>7344</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="27">
         <v>7479</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="29">
         <v>2776</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="31">
         <v>2683</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="33">
         <v>2283</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="35">
         <v>2243</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="37">
         <v>1714</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="39">
         <v>1320</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13" s="41">
         <v>999</v>
       </c>
-      <c r="N13" s="40">
+      <c r="N13" s="43">
         <v>557</v>
       </c>
-      <c r="O13" s="42">
+      <c r="O13" s="45">
         <v>248</v>
       </c>
-      <c r="P13" s="44">
+      <c r="P13" s="47">
         <v>1421</v>
       </c>
-      <c r="Q13" s="46">
+      <c r="Q13" s="49">
         <v>1373</v>
       </c>
-      <c r="R13" s="48">
+      <c r="R13" s="51">
         <v>1107</v>
       </c>
-      <c r="S13" s="50">
+      <c r="S13" s="53">
         <v>1092</v>
       </c>
-      <c r="T13" s="52">
+      <c r="T13" s="55">
         <v>861</v>
       </c>
-      <c r="U13" s="54">
+      <c r="U13" s="57">
         <v>624</v>
       </c>
-      <c r="V13" s="56">
+      <c r="V13" s="59">
         <v>483</v>
       </c>
-      <c r="W13" s="58">
+      <c r="W13" s="61">
         <v>269</v>
       </c>
-      <c r="X13" s="60">
+      <c r="X13" s="63">
         <v>114</v>
       </c>
-      <c r="Y13" s="62">
+      <c r="Y13" s="65">
         <v>1355</v>
       </c>
-      <c r="Z13" s="64">
+      <c r="Z13" s="67">
         <v>1310</v>
       </c>
-      <c r="AA13" s="66">
+      <c r="AA13" s="69">
         <v>1176</v>
       </c>
-      <c r="AB13" s="68">
+      <c r="AB13" s="71">
         <v>1151</v>
       </c>
-      <c r="AC13" s="70">
+      <c r="AC13" s="73">
         <v>853</v>
       </c>
-      <c r="AD13" s="72">
+      <c r="AD13" s="75">
         <v>696</v>
       </c>
-      <c r="AE13" s="74">
+      <c r="AE13" s="77">
         <v>516</v>
       </c>
-      <c r="AF13" s="76">
+      <c r="AF13" s="79">
         <v>288</v>
       </c>
-      <c r="AG13" s="78">
+      <c r="AG13" s="81">
         <v>134</v>
       </c>
     </row>
@@ -3178,200 +3316,200 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="25">
         <v>21758</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="27">
         <v>23012</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="29">
         <v>6527</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="31">
         <v>7528</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="33">
         <v>6856</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="35">
         <v>7100</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="37">
         <v>5652</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="39">
         <v>4427</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="41">
         <v>3783</v>
       </c>
-      <c r="N14" s="40">
+      <c r="N14" s="43">
         <v>2050</v>
       </c>
-      <c r="O14" s="42">
+      <c r="O14" s="45">
         <v>847</v>
       </c>
-      <c r="P14" s="44">
+      <c r="P14" s="47">
         <v>3256</v>
       </c>
-      <c r="Q14" s="46">
+      <c r="Q14" s="49">
         <v>3812</v>
       </c>
-      <c r="R14" s="48">
+      <c r="R14" s="51">
         <v>3505</v>
       </c>
-      <c r="S14" s="50">
+      <c r="S14" s="53">
         <v>3497</v>
       </c>
-      <c r="T14" s="52">
+      <c r="T14" s="55">
         <v>2729</v>
       </c>
-      <c r="U14" s="54">
+      <c r="U14" s="57">
         <v>1989</v>
       </c>
-      <c r="V14" s="56">
+      <c r="V14" s="59">
         <v>1650</v>
       </c>
-      <c r="W14" s="58">
+      <c r="W14" s="61">
         <v>931</v>
       </c>
-      <c r="X14" s="60">
+      <c r="X14" s="63">
         <v>389</v>
       </c>
-      <c r="Y14" s="62">
+      <c r="Y14" s="65">
         <v>3271</v>
       </c>
-      <c r="Z14" s="64">
+      <c r="Z14" s="67">
         <v>3716</v>
       </c>
-      <c r="AA14" s="66">
+      <c r="AA14" s="69">
         <v>3351</v>
       </c>
-      <c r="AB14" s="68">
+      <c r="AB14" s="71">
         <v>3603</v>
       </c>
-      <c r="AC14" s="70">
+      <c r="AC14" s="73">
         <v>2923</v>
       </c>
-      <c r="AD14" s="72">
+      <c r="AD14" s="75">
         <v>2438</v>
       </c>
-      <c r="AE14" s="74">
+      <c r="AE14" s="77">
         <v>2133</v>
       </c>
-      <c r="AF14" s="76">
+      <c r="AF14" s="79">
         <v>1119</v>
       </c>
-      <c r="AG14" s="78">
+      <c r="AG14" s="81">
         <v>458</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="26">
         <v>92281</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="28">
         <v>85481</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="30">
         <v>27730</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="32">
         <v>29161</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="34">
         <v>26965</v>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="36">
         <v>28036</v>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="38">
         <v>22678</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="40">
         <v>17503</v>
       </c>
-      <c r="M15" s="39">
+      <c r="M15" s="42">
         <v>14184</v>
       </c>
-      <c r="N15" s="41">
+      <c r="N15" s="44">
         <v>8054</v>
       </c>
-      <c r="O15" s="43">
+      <c r="O15" s="46">
         <v>3451</v>
       </c>
-      <c r="P15" s="45">
+      <c r="P15" s="48">
         <v>14004</v>
       </c>
-      <c r="Q15" s="47">
+      <c r="Q15" s="50">
         <v>15127</v>
       </c>
-      <c r="R15" s="49">
+      <c r="R15" s="52">
         <v>14433</v>
       </c>
-      <c r="S15" s="51">
+      <c r="S15" s="54">
         <v>15073</v>
       </c>
-      <c r="T15" s="53">
+      <c r="T15" s="56">
         <v>12163</v>
       </c>
-      <c r="U15" s="55">
+      <c r="U15" s="58">
         <v>8918</v>
       </c>
-      <c r="V15" s="57">
+      <c r="V15" s="60">
         <v>6961</v>
       </c>
-      <c r="W15" s="59">
+      <c r="W15" s="62">
         <v>3916</v>
       </c>
-      <c r="X15" s="61">
+      <c r="X15" s="64">
         <v>1686</v>
       </c>
-      <c r="Y15" s="63">
+      <c r="Y15" s="66">
         <v>13726</v>
       </c>
-      <c r="Z15" s="65">
+      <c r="Z15" s="68">
         <v>14034</v>
       </c>
-      <c r="AA15" s="67">
+      <c r="AA15" s="70">
         <v>12532</v>
       </c>
-      <c r="AB15" s="69">
+      <c r="AB15" s="72">
         <v>12963</v>
       </c>
-      <c r="AC15" s="71">
+      <c r="AC15" s="74">
         <v>10515</v>
       </c>
-      <c r="AD15" s="73">
+      <c r="AD15" s="76">
         <v>8585</v>
       </c>
-      <c r="AE15" s="75">
+      <c r="AE15" s="78">
         <v>7223</v>
       </c>
-      <c r="AF15" s="77">
+      <c r="AF15" s="80">
         <v>4138</v>
       </c>
-      <c r="AG15" s="79">
+      <c r="AG15" s="82">
         <v>1765</v>
       </c>
     </row>
@@ -3387,47 +3525,47 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="81.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="82.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -3452,14 +3590,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>7.01697127937337</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>4.35027793442359</v>
       </c>
-      <c r="G2" s="84">
-        <v>27.9622796227962</v>
+      <c r="G2" s="90">
+        <v>25.1993618011475</v>
       </c>
     </row>
     <row r="3">
@@ -3481,14 +3619,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>9.84251968503937</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>3.915313225058</v>
       </c>
-      <c r="G3" s="84">
-        <v>19.5797886053106</v>
+      <c r="G3" s="90">
+        <v>17.743293762207</v>
       </c>
     </row>
     <row r="4">
@@ -3510,14 +3648,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>8.0835716950628</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>2.99139972578836</v>
       </c>
-      <c r="G4" s="84">
-        <v>20.3905801263642</v>
+      <c r="G4" s="90">
+        <v>18.5332927703857</v>
       </c>
     </row>
     <row r="5">
@@ -3539,14 +3677,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>5.91173172969116</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>5.33199195171026</v>
       </c>
-      <c r="G5" s="84">
-        <v>25.9169298032548</v>
+      <c r="G5" s="90">
+        <v>23.2419548034668</v>
       </c>
     </row>
     <row r="6">
@@ -3568,14 +3706,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>3.52112676056338</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>6.58728147960476</v>
       </c>
-      <c r="G6" s="84">
-        <v>44.6200607902736</v>
+      <c r="G6" s="90">
+        <v>44.5790824890137</v>
       </c>
     </row>
     <row r="7">
@@ -3597,14 +3735,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="86">
         <v>3.72001957905042</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="88">
         <v>5.72759926220755</v>
       </c>
-      <c r="G7" s="84">
-        <v>39.0018484288355</v>
+      <c r="G7" s="90">
+        <v>36.4678344726562</v>
       </c>
     </row>
     <row r="8">
@@ -3626,14 +3764,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="86">
         <v>5.20682672837721</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="88">
         <v>5.44802867383513</v>
       </c>
-      <c r="G8" s="84">
-        <v>29.8931072613343</v>
+      <c r="G8" s="90">
+        <v>28.1215667724609</v>
       </c>
     </row>
     <row r="9">
@@ -3655,14 +3793,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="86">
         <v>5.52467110942302</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="88">
         <v>3.57848817394861</v>
       </c>
-      <c r="G9" s="84">
-        <v>24.7091526819726</v>
+      <c r="G9" s="90">
+        <v>22.1655158996582</v>
       </c>
     </row>
     <row r="10">
@@ -3684,14 +3822,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="86">
         <v>7.03748815807281</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="88">
         <v>5.80610315960032</v>
       </c>
-      <c r="G10" s="84">
-        <v>24.4047619047619</v>
+      <c r="G10" s="90">
+        <v>22.6615238189697</v>
       </c>
     </row>
     <row r="11">
@@ -3713,14 +3851,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="86">
         <v>6.62589194699286</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="88">
         <v>3.28034317436286</v>
       </c>
-      <c r="G11" s="84">
-        <v>22.6389819156062</v>
+      <c r="G11" s="90">
+        <v>25.2538070678711</v>
       </c>
     </row>
     <row r="12">
@@ -3742,14 +3880,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="86">
         <v>8.97043832823649</v>
       </c>
-      <c r="F12" s="82">
+      <c r="F12" s="88">
         <v>8.01314978426135</v>
       </c>
-      <c r="G12" s="84">
-        <v>25.905547913801</v>
+      <c r="G12" s="90">
+        <v>26.2944164276123</v>
       </c>
     </row>
     <row r="13">
@@ -3771,14 +3909,14 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="86">
         <v>13.8586956521739</v>
       </c>
-      <c r="F13" s="82">
+      <c r="F13" s="88">
         <v>6.09633549943056</v>
       </c>
-      <c r="G13" s="84">
-        <v>20.6201033505584</v>
+      <c r="G13" s="90">
+        <v>19.6537685394287</v>
       </c>
     </row>
     <row r="14">
@@ -3800,107 +3938,107 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="86">
         <v>8.00323940642641</v>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="88">
         <v>6.56920357364674</v>
       </c>
-      <c r="G14" s="84">
-        <v>26.7033481620229</v>
+      <c r="G14" s="90">
+        <v>24.7192420959473</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="87">
         <v>7.6106695153783</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="89">
         <v>5.15478039829069</v>
       </c>
-      <c r="G15" s="85">
-        <v>25.7972055824039</v>
+      <c r="G15" s="91">
+        <v>23.9348972325861</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="87">
         <v>7.88520580382868</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="89">
         <v>5.13999885007764</v>
       </c>
-      <c r="G16" s="85">
-        <v>26.3837840326381</v>
+      <c r="G16" s="91">
+        <v>24.6272584356484</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G17" s="85">
-        <v>32.052654940463</v>
+      <c r="G17" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -3915,47 +4053,47 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="81.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="82.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -3980,13 +4118,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>2.17551981546151</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>2.80165570863245</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>1.93706387546967</v>
       </c>
     </row>
@@ -4009,13 +4147,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>0.886908660497456</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>1.88944636848504</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>0</v>
       </c>
     </row>
@@ -4038,13 +4176,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>1.95818088831189</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>1.18641439205955</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>2.43220930970979</v>
       </c>
     </row>
@@ -4067,13 +4205,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>2.5117673995459</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>1.66240829560566</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>2.92924233234318</v>
       </c>
     </row>
@@ -4096,13 +4234,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>0</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>0</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>0</v>
       </c>
     </row>
@@ -4125,13 +4263,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="95">
         <v>0.0609002647837604</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="97">
         <v>0.10790860610231</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="99">
         <v>0</v>
       </c>
     </row>
@@ -4154,13 +4292,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="95">
         <v>0.477668688035422</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="97">
         <v>0.532892319000367</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="99">
         <v>0.441934205311137</v>
       </c>
     </row>
@@ -4183,13 +4321,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="95">
         <v>0</v>
       </c>
-      <c r="F9" s="88">
+      <c r="F9" s="97">
         <v>0</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="99">
         <v>0</v>
       </c>
     </row>
@@ -4212,13 +4350,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="95">
         <v>1.42120663488516</v>
       </c>
-      <c r="F10" s="88">
+      <c r="F10" s="97">
         <v>3.13996162019698</v>
       </c>
-      <c r="G10" s="90">
+      <c r="G10" s="99">
         <v>0</v>
       </c>
     </row>
@@ -4241,13 +4379,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="95">
         <v>2.02962798773505</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="97">
         <v>2.85824813484388</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="99">
         <v>0.358814352574102</v>
       </c>
     </row>
@@ -4270,13 +4408,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="95">
         <v>1.47266651477178</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="97">
         <v>1.27220979716087</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="99">
         <v>1.60147303184084</v>
       </c>
     </row>
@@ -4299,13 +4437,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="95">
         <v>2.32854891751165</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="97">
         <v>1.33001498608435</v>
       </c>
-      <c r="G13" s="90">
+      <c r="G13" s="99">
         <v>2.7984886649874</v>
       </c>
     </row>
@@ -4328,106 +4466,106 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="95">
         <v>2.4615871972961</v>
       </c>
-      <c r="F14" s="88">
+      <c r="F14" s="97">
         <v>2.21676093838762</v>
       </c>
-      <c r="G14" s="90">
+      <c r="G14" s="99">
         <v>3.15419171372896</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="96">
         <v>1.44969519597397</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="98">
         <v>1.47816073098033</v>
       </c>
-      <c r="G15" s="91">
+      <c r="G15" s="100">
         <v>1.47751310469842</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN NORTE (por población)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="87">
+      <c r="E16" s="96">
         <v>1.82462249111888</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="98">
         <v>1.50531530154741</v>
       </c>
-      <c r="G16" s="91">
+      <c r="G16" s="100">
         <v>2.24897326039897</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E17" s="87">
+      <c r="E17" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G17" s="91">
+      <c r="G17" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -4443,23 +4581,23 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -4646,35 +4784,35 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -4939,22 +5077,23 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -5141,23 +5280,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -5445,17 +5584,17 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -5468,7 +5607,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>27.9622796227962</v>
+        <v>25.1993618011475</v>
       </c>
     </row>
     <row r="3">
@@ -5478,7 +5617,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>19.5797886053106</v>
+        <v>17.743293762207</v>
       </c>
     </row>
     <row r="4">
@@ -5488,7 +5627,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>20.3905801263642</v>
+        <v>18.5332927703857</v>
       </c>
     </row>
     <row r="5">
@@ -5498,7 +5637,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>25.9169298032548</v>
+        <v>23.2419548034668</v>
       </c>
     </row>
     <row r="6">
@@ -5508,7 +5647,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>44.6200607902736</v>
+        <v>44.5790824890137</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5657,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>39.0018484288355</v>
+        <v>36.4678344726562</v>
       </c>
     </row>
     <row r="8">
@@ -5528,7 +5667,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>29.8931072613343</v>
+        <v>28.1215667724609</v>
       </c>
     </row>
     <row r="9">
@@ -5538,7 +5677,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>24.7091526819726</v>
+        <v>22.1655158996582</v>
       </c>
     </row>
     <row r="10">
@@ -5548,7 +5687,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>24.4047619047619</v>
+        <v>22.6615238189697</v>
       </c>
     </row>
     <row r="11">
@@ -5558,7 +5697,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>22.6389819156062</v>
+        <v>25.2538070678711</v>
       </c>
     </row>
     <row r="12">
@@ -5568,7 +5707,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>25.905547913801</v>
+        <v>26.2944164276123</v>
       </c>
     </row>
     <row r="13">
@@ -5578,7 +5717,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>20.6201033505584</v>
+        <v>19.6537685394287</v>
       </c>
     </row>
     <row r="14">
@@ -5588,7 +5727,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>26.7033481620229</v>
+        <v>24.7192420959473</v>
       </c>
     </row>
   </sheetData>
